--- a/data/trans_orig/P1409-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P1409-Provincia-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de asma en 2012</t>
+          <t>Población con diagnóstico de asma en 2012 (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3585</t>
+          <t>3706</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>14705</t>
+          <t>14909</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>6067</t>
+          <t>5877</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>20791</t>
+          <t>21323</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>11523</t>
+          <t>12013</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>29218</t>
+          <t>29918</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>5,14%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>280033</t>
+          <t>279829</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>291153</t>
+          <t>291032</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,01%</t>
+          <t>94,94%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,78%</t>
+          <t>98,74%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>266454</t>
+          <t>265922</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>281178</t>
+          <t>281368</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>92,76%</t>
+          <t>92,58%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,89%</t>
+          <t>97,95%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>552765</t>
+          <t>552065</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>570460</t>
+          <t>569970</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,98%</t>
+          <t>94,86%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,02%</t>
+          <t>97,94%</t>
         </is>
       </c>
     </row>
@@ -1075,12 +1075,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2883</t>
+          <t>2099</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13595</t>
+          <t>12251</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1090,12 +1090,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1110,12 +1110,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>10358</t>
+          <t>10799</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>28016</t>
+          <t>29167</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1125,12 +1125,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>15353</t>
+          <t>15605</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>35261</t>
+          <t>36128</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,51%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>491932</t>
+          <t>493276</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>502644</t>
+          <t>503428</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,31%</t>
+          <t>97,58%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,43%</t>
+          <t>99,58%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>495749</t>
+          <t>494598</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>513407</t>
+          <t>512966</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,65%</t>
+          <t>94,43%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,02%</t>
+          <t>97,94%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>994031</t>
+          <t>993164</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1013939</t>
+          <t>1013687</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,57%</t>
+          <t>96,49%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,51%</t>
+          <t>98,48%</t>
         </is>
       </c>
     </row>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>2033</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>11926</t>
+          <t>12082</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1433,12 +1433,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1453,12 +1453,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2952</t>
+          <t>2970</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>15927</t>
+          <t>15664</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1473,7 +1473,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>6842</t>
+          <t>6988</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>22040</t>
+          <t>21316</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,12 +1503,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,21%</t>
         </is>
       </c>
     </row>
@@ -1531,12 +1531,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>312120</t>
+          <t>311964</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>322046</t>
+          <t>322013</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,32%</t>
+          <t>96,27%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,38%</t>
+          <t>99,37%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1566,12 +1566,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>325093</t>
+          <t>325356</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>338068</t>
+          <t>338050</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,33%</t>
+          <t>95,41%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>643026</t>
+          <t>643750</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>658224</t>
+          <t>658078</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,69%</t>
+          <t>96,79%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,97%</t>
+          <t>98,95%</t>
         </is>
       </c>
     </row>
@@ -1761,12 +1761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3054</t>
+          <t>3235</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>13913</t>
+          <t>14315</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1776,12 +1776,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1796,12 +1796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3990</t>
+          <t>3950</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>16242</t>
+          <t>16314</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1811,12 +1811,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>9696</t>
+          <t>10102</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>25157</t>
+          <t>25046</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,28%</t>
         </is>
       </c>
     </row>
@@ -1874,12 +1874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>360069</t>
+          <t>359667</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>370928</t>
+          <t>370747</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1889,12 +1889,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,28%</t>
+          <t>96,17%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,18%</t>
+          <t>99,14%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>372709</t>
+          <t>372637</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>384961</t>
+          <t>385001</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1924,12 +1924,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,82%</t>
+          <t>95,81%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,97%</t>
+          <t>98,98%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>737776</t>
+          <t>737887</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>753237</t>
+          <t>752831</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,7%</t>
+          <t>96,72%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,73%</t>
+          <t>98,68%</t>
         </is>
       </c>
     </row>
@@ -2104,12 +2104,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1849</t>
+          <t>1954</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>11225</t>
+          <t>11638</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2139,12 +2139,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1984</t>
+          <t>1928</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>13731</t>
+          <t>13204</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2154,12 +2154,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>5621</t>
+          <t>4925</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>19094</t>
+          <t>18518</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2189,12 +2189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,28%</t>
         </is>
       </c>
     </row>
@@ -2217,12 +2217,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>201393</t>
+          <t>200980</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>210769</t>
+          <t>210664</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>94,72%</t>
+          <t>94,53%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,13%</t>
+          <t>99,08%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2252,12 +2252,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>205860</t>
+          <t>206387</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>217607</t>
+          <t>217663</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2267,12 +2267,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>93,75%</t>
+          <t>93,99%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,1%</t>
+          <t>99,12%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>413115</t>
+          <t>413691</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>426588</t>
+          <t>427284</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,12 +2302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,58%</t>
+          <t>95,72%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,7%</t>
+          <t>98,86%</t>
         </is>
       </c>
     </row>
@@ -2447,12 +2447,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3044</t>
+          <t>3016</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>14306</t>
+          <t>13483</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2462,12 +2462,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2482,12 +2482,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>4038</t>
+          <t>4018</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>16254</t>
+          <t>15825</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2497,12 +2497,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2517,12 +2517,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>9143</t>
+          <t>9906</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>24485</t>
+          <t>25995</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2532,12 +2532,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,71%</t>
         </is>
       </c>
     </row>
@@ -2560,12 +2560,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>259675</t>
+          <t>260498</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>270937</t>
+          <t>270965</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2575,12 +2575,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>94,78%</t>
+          <t>95,08%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,89%</t>
+          <t>98,9%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2595,12 +2595,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>261842</t>
+          <t>262271</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>274058</t>
+          <t>274078</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2610,12 +2610,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>94,16%</t>
+          <t>94,31%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>98,55%</t>
+          <t>98,56%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2630,12 +2630,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>527592</t>
+          <t>526082</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>542934</t>
+          <t>542171</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2645,12 +2645,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>95,56%</t>
+          <t>95,29%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,34%</t>
+          <t>98,21%</t>
         </is>
       </c>
     </row>
@@ -2790,12 +2790,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>4826</t>
+          <t>4834</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>18702</t>
+          <t>18751</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2825,12 +2825,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>7888</t>
+          <t>7908</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>26296</t>
+          <t>25636</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2845,7 +2845,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2860,12 +2860,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>15596</t>
+          <t>15927</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>39071</t>
+          <t>37928</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2875,12 +2875,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,8%</t>
         </is>
       </c>
     </row>
@@ -2903,12 +2903,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>644086</t>
+          <t>644037</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>657962</t>
+          <t>657954</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2918,7 +2918,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>97,18%</t>
+          <t>97,17%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2938,12 +2938,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>667557</t>
+          <t>668217</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>685965</t>
+          <t>685945</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2953,7 +2953,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>96,21%</t>
+          <t>96,31%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -2973,12 +2973,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1317570</t>
+          <t>1318713</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1341045</t>
+          <t>1340714</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2988,12 +2988,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>97,12%</t>
+          <t>97,2%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,85%</t>
+          <t>98,83%</t>
         </is>
       </c>
     </row>
@@ -3133,12 +3133,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>9792</t>
+          <t>9331</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>26953</t>
+          <t>27041</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3148,12 +3148,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3168,12 +3168,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>13383</t>
+          <t>13830</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>31941</t>
+          <t>33501</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3183,12 +3183,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3203,12 +3203,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>26998</t>
+          <t>27658</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>53634</t>
+          <t>52721</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3218,12 +3218,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,29%</t>
         </is>
       </c>
     </row>
@@ -3246,12 +3246,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>752145</t>
+          <t>752057</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>769306</t>
+          <t>769767</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3261,12 +3261,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>96,54%</t>
+          <t>96,53%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>98,74%</t>
+          <t>98,8%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>789454</t>
+          <t>787894</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>808012</t>
+          <t>807565</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3296,12 +3296,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>96,11%</t>
+          <t>95,92%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>98,37%</t>
+          <t>98,32%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3316,12 +3316,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1546859</t>
+          <t>1547772</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1573495</t>
+          <t>1572835</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3331,12 +3331,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>96,65%</t>
+          <t>96,71%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>98,31%</t>
+          <t>98,27%</t>
         </is>
       </c>
     </row>
@@ -3476,12 +3476,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>50376</t>
+          <t>51408</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>85223</t>
+          <t>84834</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3491,12 +3491,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3511,12 +3511,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>77457</t>
+          <t>78185</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>117167</t>
+          <t>119660</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3526,12 +3526,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3546,12 +3546,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>136242</t>
+          <t>139010</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>189056</t>
+          <t>190369</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3561,12 +3561,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,73%</t>
         </is>
       </c>
     </row>
@@ -3589,12 +3589,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3341556</t>
+          <t>3341945</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3376403</t>
+          <t>3375371</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3604,12 +3604,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>97,51%</t>
+          <t>97,52%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>98,53%</t>
+          <t>98,5%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3624,12 +3624,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3436749</t>
+          <t>3434256</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3476459</t>
+          <t>3475731</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3639,12 +3639,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>96,7%</t>
+          <t>96,63%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>97,82%</t>
+          <t>97,8%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3659,12 +3659,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6791638</t>
+          <t>6790325</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6844452</t>
+          <t>6841684</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3674,12 +3674,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>97,29%</t>
+          <t>97,27%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>98,05%</t>
+          <t>98,01%</t>
         </is>
       </c>
     </row>
@@ -3860,7 +3860,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de asma en 2016</t>
+          <t>Población con diagnóstico de asma en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4055,12 +4055,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5253</t>
+          <t>5556</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>18036</t>
+          <t>19743</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4090,12 +4090,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5138</t>
+          <t>5571</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>18178</t>
+          <t>18582</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,44%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4125,12 +4125,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>13392</t>
+          <t>12622</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>32010</t>
+          <t>31553</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4140,12 +4140,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,42%</t>
         </is>
       </c>
     </row>
@@ -4168,12 +4168,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>275725</t>
+          <t>274018</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>288508</t>
+          <t>288205</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,86%</t>
+          <t>93,28%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,21%</t>
+          <t>98,11%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>270525</t>
+          <t>270121</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>283565</t>
+          <t>283132</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,7%</t>
+          <t>93,56%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,22%</t>
+          <t>98,07%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4238,12 +4238,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>550454</t>
+          <t>550911</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>569072</t>
+          <t>569842</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4253,12 +4253,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,5%</t>
+          <t>94,58%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,7%</t>
+          <t>97,83%</t>
         </is>
       </c>
     </row>
@@ -4398,12 +4398,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2152</t>
+          <t>1846</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>12714</t>
+          <t>12719</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4413,7 +4413,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>11308</t>
+          <t>11290</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>28066</t>
+          <t>28436</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4453,7 +4453,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>16564</t>
+          <t>15270</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>35120</t>
+          <t>35380</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4483,12 +4483,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,45%</t>
         </is>
       </c>
     </row>
@@ -4511,12 +4511,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>489861</t>
+          <t>489856</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>500423</t>
+          <t>500729</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4531,7 +4531,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,57%</t>
+          <t>99,63%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4546,12 +4546,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>495018</t>
+          <t>494648</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>511776</t>
+          <t>511794</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4561,7 +4561,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,63%</t>
+          <t>94,56%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -4581,12 +4581,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>990539</t>
+          <t>990279</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1009095</t>
+          <t>1010389</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,58%</t>
+          <t>96,55%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,39%</t>
+          <t>98,51%</t>
         </is>
       </c>
     </row>
@@ -4741,12 +4741,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2560</t>
+          <t>2497</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>12950</t>
+          <t>13201</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4756,12 +4756,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5710</t>
+          <t>6135</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>20742</t>
+          <t>20750</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4791,7 +4791,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>10643</t>
+          <t>10548</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>28926</t>
+          <t>29173</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,45%</t>
         </is>
       </c>
     </row>
@@ -4854,12 +4854,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>305615</t>
+          <t>305364</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>316005</t>
+          <t>316068</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4869,12 +4869,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,93%</t>
+          <t>95,86%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,2%</t>
+          <t>99,22%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>315567</t>
+          <t>315559</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>330599</t>
+          <t>330174</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4909,7 +4909,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,3%</t>
+          <t>98,18%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>625948</t>
+          <t>625701</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>644231</t>
+          <t>644326</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,58%</t>
+          <t>95,55%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,37%</t>
+          <t>98,39%</t>
         </is>
       </c>
     </row>
@@ -5084,12 +5084,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>9005</t>
+          <t>8475</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>25183</t>
+          <t>24588</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>12187</t>
+          <t>12344</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>28840</t>
+          <t>30402</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5134,12 +5134,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>7,85%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>25961</t>
+          <t>25279</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>50092</t>
+          <t>48330</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5169,12 +5169,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>6,38%</t>
         </is>
       </c>
     </row>
@@ -5197,12 +5197,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>344781</t>
+          <t>345376</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>360959</t>
+          <t>361489</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5212,12 +5212,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,19%</t>
+          <t>93,35%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,57%</t>
+          <t>97,71%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>358443</t>
+          <t>356881</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>375096</t>
+          <t>374939</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5247,12 +5247,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,55%</t>
+          <t>92,15%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,85%</t>
+          <t>96,81%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>707155</t>
+          <t>708917</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>731286</t>
+          <t>731968</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5282,12 +5282,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,38%</t>
+          <t>93,62%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,57%</t>
+          <t>96,66%</t>
         </is>
       </c>
     </row>
@@ -5427,12 +5427,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1993</t>
+          <t>1974</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>11886</t>
+          <t>11275</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5442,12 +5442,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2843</t>
+          <t>2980</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>13071</t>
+          <t>13223</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5477,12 +5477,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>6621</t>
+          <t>6374</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>20003</t>
+          <t>19087</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,44%</t>
         </is>
       </c>
     </row>
@@ -5540,12 +5540,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>199335</t>
+          <t>199946</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>209228</t>
+          <t>209247</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5555,12 +5555,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>94,37%</t>
+          <t>94,66%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,06%</t>
+          <t>99,07%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>205516</t>
+          <t>205364</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>215744</t>
+          <t>215607</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>94,02%</t>
+          <t>93,95%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,7%</t>
+          <t>98,64%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>409805</t>
+          <t>410721</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>423187</t>
+          <t>423434</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5625,12 +5625,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,35%</t>
+          <t>95,56%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,46%</t>
+          <t>98,52%</t>
         </is>
       </c>
     </row>
@@ -5770,12 +5770,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>879</t>
+          <t>833</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8527</t>
+          <t>8688</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5785,12 +5785,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>3916</t>
+          <t>3887</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>16207</t>
+          <t>15989</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5820,12 +5820,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>6279</t>
+          <t>6413</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>19715</t>
+          <t>19907</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5855,12 +5855,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,71%</t>
         </is>
       </c>
     </row>
@@ -5883,12 +5883,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>254596</t>
+          <t>254435</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>262244</t>
+          <t>262290</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5898,12 +5898,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>96,76%</t>
+          <t>96,7%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,67%</t>
+          <t>99,68%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>256908</t>
+          <t>257126</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>269199</t>
+          <t>269228</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5933,12 +5933,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>94,07%</t>
+          <t>94,15%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>98,57%</t>
+          <t>98,58%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>516523</t>
+          <t>516331</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>529959</t>
+          <t>529825</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5968,12 +5968,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>96,32%</t>
+          <t>96,29%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,83%</t>
+          <t>98,8%</t>
         </is>
       </c>
     </row>
@@ -6113,12 +6113,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>11823</t>
+          <t>12820</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>31346</t>
+          <t>32634</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>21356</t>
+          <t>20508</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>43680</t>
+          <t>43500</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>37323</t>
+          <t>38411</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>67903</t>
+          <t>68005</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6198,12 +6198,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>5,05%</t>
         </is>
       </c>
     </row>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>625212</t>
+          <t>623924</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>644735</t>
+          <t>643738</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>95,23%</t>
+          <t>95,03%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,2%</t>
+          <t>98,05%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>647614</t>
+          <t>647794</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>669938</t>
+          <t>670786</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>93,68%</t>
+          <t>93,71%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>96,91%</t>
+          <t>97,03%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1279949</t>
+          <t>1279847</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1310529</t>
+          <t>1309441</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6311,12 +6311,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>94,96%</t>
+          <t>94,95%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>97,23%</t>
+          <t>97,15%</t>
         </is>
       </c>
     </row>
@@ -6456,12 +6456,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>11262</t>
+          <t>11823</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>27237</t>
+          <t>27864</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6491,12 +6491,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>22824</t>
+          <t>24296</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>47903</t>
+          <t>50150</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6506,12 +6506,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6526,12 +6526,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>39977</t>
+          <t>38794</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>69056</t>
+          <t>70896</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6541,12 +6541,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,42%</t>
         </is>
       </c>
     </row>
@@ -6569,12 +6569,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>751346</t>
+          <t>750719</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>767321</t>
+          <t>766760</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6584,12 +6584,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>96,5%</t>
+          <t>96,42%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>98,55%</t>
+          <t>98,48%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6604,12 +6604,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>778264</t>
+          <t>776017</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>803343</t>
+          <t>801871</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6619,12 +6619,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>94,2%</t>
+          <t>93,93%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>97,24%</t>
+          <t>97,06%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6639,12 +6639,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1535694</t>
+          <t>1533854</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1564773</t>
+          <t>1565956</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6654,12 +6654,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>95,7%</t>
+          <t>95,58%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>97,51%</t>
+          <t>97,58%</t>
         </is>
       </c>
     </row>
@@ -6799,12 +6799,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>68886</t>
+          <t>68851</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>104366</t>
+          <t>106386</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6819,7 +6819,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6834,12 +6834,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>117063</t>
+          <t>119238</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>165585</t>
+          <t>166235</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6849,12 +6849,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6869,12 +6869,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>197780</t>
+          <t>200126</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>257364</t>
+          <t>260204</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6884,12 +6884,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,75%</t>
         </is>
       </c>
     </row>
@@ -6912,12 +6912,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3289984</t>
+          <t>3287964</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3325464</t>
+          <t>3325499</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6927,7 +6927,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>96,93%</t>
+          <t>96,87%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -6947,12 +6947,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3378957</t>
+          <t>3378307</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3427479</t>
+          <t>3425304</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6962,12 +6962,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>95,33%</t>
+          <t>95,31%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>96,7%</t>
+          <t>96,64%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6982,12 +6982,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6681528</t>
+          <t>6678688</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6741112</t>
+          <t>6738766</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6997,12 +6997,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>96,29%</t>
+          <t>96,25%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>97,15%</t>
+          <t>97,12%</t>
         </is>
       </c>
     </row>
@@ -7183,7 +7183,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de asma en 2023</t>
+          <t>Población con diagnóstico de asma en 2023 (tasa de respuesta: 99,87%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -7378,12 +7378,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5558</t>
+          <t>5973</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>31967</t>
+          <t>30394</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7393,12 +7393,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>10,26%</t>
+          <t>9,76%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7413,12 +7413,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>7740</t>
+          <t>7547</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>18399</t>
+          <t>18189</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7428,12 +7428,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7448,12 +7448,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>16658</t>
+          <t>16498</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>43743</t>
+          <t>41454</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7463,12 +7463,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>6,9%</t>
         </is>
       </c>
     </row>
@@ -7491,12 +7491,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>279476</t>
+          <t>281049</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>305885</t>
+          <t>305470</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7506,12 +7506,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>89,74%</t>
+          <t>90,24%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,22%</t>
+          <t>98,08%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7526,12 +7526,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>271236</t>
+          <t>271446</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>281895</t>
+          <t>282088</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7541,12 +7541,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,65%</t>
+          <t>93,72%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,33%</t>
+          <t>97,39%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7561,12 +7561,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>557334</t>
+          <t>559623</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>584419</t>
+          <t>584579</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7576,12 +7576,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>92,72%</t>
+          <t>93,1%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,23%</t>
+          <t>97,26%</t>
         </is>
       </c>
     </row>
@@ -7721,12 +7721,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>15121</t>
+          <t>13397</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>47172</t>
+          <t>41654</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7736,12 +7736,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7756,12 +7756,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>16384</t>
+          <t>16631</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>33052</t>
+          <t>31915</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7771,12 +7771,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7791,12 +7791,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>33722</t>
+          <t>33860</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>65512</t>
+          <t>64574</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7806,12 +7806,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,27%</t>
         </is>
       </c>
     </row>
@@ -7834,12 +7834,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>470221</t>
+          <t>475739</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>502272</t>
+          <t>503996</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7849,12 +7849,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>90,88%</t>
+          <t>91,95%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,08%</t>
+          <t>97,41%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7869,12 +7869,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>480133</t>
+          <t>481270</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>496801</t>
+          <t>496554</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7884,12 +7884,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,56%</t>
+          <t>93,78%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,81%</t>
+          <t>96,76%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7904,12 +7904,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>965066</t>
+          <t>966004</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>996856</t>
+          <t>996718</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7919,12 +7919,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,64%</t>
+          <t>93,73%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,73%</t>
+          <t>96,71%</t>
         </is>
       </c>
     </row>
@@ -8064,12 +8064,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7842</t>
+          <t>7933</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>20901</t>
+          <t>20983</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8079,12 +8079,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8099,12 +8099,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>11739</t>
+          <t>11610</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>25907</t>
+          <t>25910</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8114,7 +8114,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -8134,12 +8134,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>22993</t>
+          <t>23090</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>42492</t>
+          <t>42305</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8149,12 +8149,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>6,36%</t>
         </is>
       </c>
     </row>
@@ -8177,12 +8177,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>295149</t>
+          <t>295067</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>308208</t>
+          <t>308117</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8192,12 +8192,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,39%</t>
+          <t>93,36%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,52%</t>
+          <t>97,49%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8212,12 +8212,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>323221</t>
+          <t>323218</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>337389</t>
+          <t>337518</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8232,7 +8232,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,64%</t>
+          <t>96,67%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8247,12 +8247,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>622686</t>
+          <t>622873</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>642185</t>
+          <t>642088</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8262,12 +8262,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>93,61%</t>
+          <t>93,64%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,54%</t>
+          <t>96,53%</t>
         </is>
       </c>
     </row>
@@ -8407,12 +8407,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5962</t>
+          <t>5900</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>25414</t>
+          <t>29131</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8422,12 +8422,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>9,32%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8442,12 +8442,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>6248</t>
+          <t>6228</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>224286</t>
+          <t>227878</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8462,7 +8462,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>47,15%</t>
+          <t>47,9%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8477,12 +8477,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>17425</t>
+          <t>17353</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>286389</t>
+          <t>270810</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8492,12 +8492,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>36,33%</t>
+          <t>34,35%</t>
         </is>
       </c>
     </row>
@@ -8520,12 +8520,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>287143</t>
+          <t>283426</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>306595</t>
+          <t>306657</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8535,12 +8535,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>91,87%</t>
+          <t>90,68%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,09%</t>
+          <t>98,11%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8555,12 +8555,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>251432</t>
+          <t>247840</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>469470</t>
+          <t>469490</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8570,7 +8570,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>52,85%</t>
+          <t>52,1%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -8590,12 +8590,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>501885</t>
+          <t>517464</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>770849</t>
+          <t>770921</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8605,12 +8605,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>63,67%</t>
+          <t>65,65%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,79%</t>
+          <t>97,8%</t>
         </is>
       </c>
     </row>
@@ -8750,12 +8750,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>833</t>
+          <t>838</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>9445</t>
+          <t>9165</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8770,7 +8770,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8785,12 +8785,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>6011</t>
+          <t>6640</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>17359</t>
+          <t>19114</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8800,12 +8800,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>9,21%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8820,12 +8820,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>8497</t>
+          <t>8346</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>23347</t>
+          <t>21818</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8835,12 +8835,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>5,65%</t>
         </is>
       </c>
     </row>
@@ -8863,12 +8863,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>169297</t>
+          <t>169577</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>177909</t>
+          <t>177904</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8878,7 +8878,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>94,72%</t>
+          <t>94,87%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -8898,12 +8898,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>190083</t>
+          <t>188328</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>201431</t>
+          <t>200802</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8913,12 +8913,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>91,63%</t>
+          <t>90,79%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,1%</t>
+          <t>96,8%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8933,12 +8933,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>362837</t>
+          <t>364366</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>377687</t>
+          <t>377838</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8948,12 +8948,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>93,95%</t>
+          <t>94,35%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,8%</t>
+          <t>97,84%</t>
         </is>
       </c>
     </row>
@@ -9093,12 +9093,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>5934</t>
+          <t>5554</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>15814</t>
+          <t>15872</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9108,12 +9108,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9128,12 +9128,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>9382</t>
+          <t>9372</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>20915</t>
+          <t>20061</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9148,7 +9148,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9163,12 +9163,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>17388</t>
+          <t>17516</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>31430</t>
+          <t>32516</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9178,12 +9178,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>6,18%</t>
         </is>
       </c>
     </row>
@@ -9206,12 +9206,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>253822</t>
+          <t>253764</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>263702</t>
+          <t>264082</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9221,12 +9221,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>94,13%</t>
+          <t>94,11%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>97,8%</t>
+          <t>97,94%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9241,12 +9241,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>235472</t>
+          <t>236326</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>247005</t>
+          <t>247015</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9256,7 +9256,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>91,84%</t>
+          <t>92,18%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -9276,12 +9276,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>494593</t>
+          <t>493507</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>508635</t>
+          <t>508507</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9291,12 +9291,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>94,03%</t>
+          <t>93,82%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>96,69%</t>
+          <t>96,67%</t>
         </is>
       </c>
     </row>
@@ -9436,12 +9436,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>14024</t>
+          <t>13656</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>40648</t>
+          <t>40748</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9451,12 +9451,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9471,12 +9471,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>20864</t>
+          <t>24111</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>69688</t>
+          <t>70040</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9486,12 +9486,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>8,25%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9506,12 +9506,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>42643</t>
+          <t>46650</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>92022</t>
+          <t>96674</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9521,12 +9521,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,58%</t>
         </is>
       </c>
     </row>
@@ -9549,12 +9549,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>580658</t>
+          <t>580558</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>607282</t>
+          <t>607650</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9564,12 +9564,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>93,46%</t>
+          <t>93,44%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,74%</t>
+          <t>97,8%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9579,17 +9579,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>799626</t>
+          <t>799627</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>778785</t>
+          <t>778434</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>827609</t>
+          <t>824363</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9599,12 +9599,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>91,79%</t>
+          <t>91,75%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>97,54%</t>
+          <t>97,16%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9619,12 +9619,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1377758</t>
+          <t>1373106</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1427137</t>
+          <t>1423130</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9634,12 +9634,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>93,74%</t>
+          <t>93,42%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>97,1%</t>
+          <t>96,83%</t>
         </is>
       </c>
     </row>
@@ -9692,17 +9692,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>848473</t>
+          <t>848474</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>848473</t>
+          <t>848474</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>848473</t>
+          <t>848474</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -9779,12 +9779,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>11276</t>
+          <t>12118</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>45167</t>
+          <t>45326</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9794,12 +9794,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9819,7 +9819,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>36050</t>
+          <t>35859</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9834,7 +9834,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9849,12 +9849,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>31888</t>
+          <t>33713</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>73663</t>
+          <t>71120</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9864,12 +9864,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,33%</t>
         </is>
       </c>
     </row>
@@ -9892,12 +9892,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>883553</t>
+          <t>883394</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>917444</t>
+          <t>916602</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9907,12 +9907,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>95,14%</t>
+          <t>95,12%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>98,79%</t>
+          <t>98,7%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9927,7 +9927,7 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>679342</t>
+          <t>679533</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
@@ -9942,7 +9942,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>94,96%</t>
+          <t>94,99%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -9962,12 +9962,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1570449</t>
+          <t>1572992</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1612224</t>
+          <t>1610399</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9977,12 +9977,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>95,52%</t>
+          <t>95,67%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>98,06%</t>
+          <t>97,95%</t>
         </is>
       </c>
     </row>
@@ -10122,12 +10122,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>94673</t>
+          <t>95309</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>157388</t>
+          <t>159198</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10137,12 +10137,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10157,12 +10157,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>153764</t>
+          <t>152418</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>476073</t>
+          <t>508248</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10172,12 +10172,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>13,02%</t>
+          <t>13,9%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10192,12 +10192,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>273537</t>
+          <t>273464</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>630304</t>
+          <t>620534</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10212,7 +10212,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>8,73%</t>
         </is>
       </c>
     </row>
@@ -10235,12 +10235,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3298459</t>
+          <t>3296649</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3361174</t>
+          <t>3360538</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10250,12 +10250,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>95,45%</t>
+          <t>95,39%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>97,26%</t>
+          <t>97,24%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10270,12 +10270,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3179286</t>
+          <t>3147111</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3501595</t>
+          <t>3502941</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10285,12 +10285,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>86,98%</t>
+          <t>86,1%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>95,79%</t>
+          <t>95,83%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10305,12 +10305,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6480903</t>
+          <t>6490673</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6837670</t>
+          <t>6837743</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10320,7 +10320,7 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>91,14%</t>
+          <t>91,27%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">

--- a/data/trans_orig/P1409-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P1409-Provincia-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3706</t>
+          <t>3320</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>14909</t>
+          <t>14516</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5877</t>
+          <t>5328</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>21323</t>
+          <t>19272</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>12013</t>
+          <t>11704</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>29918</t>
+          <t>29637</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,09%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>279829</t>
+          <t>280222</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>291032</t>
+          <t>291418</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,94%</t>
+          <t>95,07%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,74%</t>
+          <t>98,87%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>265922</t>
+          <t>267973</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>281368</t>
+          <t>281917</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>92,58%</t>
+          <t>93,29%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,95%</t>
+          <t>98,15%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>552065</t>
+          <t>552346</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>569970</t>
+          <t>570279</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,86%</t>
+          <t>94,91%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,94%</t>
+          <t>97,99%</t>
         </is>
       </c>
     </row>
@@ -1075,12 +1075,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2099</t>
+          <t>2916</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>12251</t>
+          <t>13247</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1090,12 +1090,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1110,12 +1110,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>10799</t>
+          <t>10519</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>29167</t>
+          <t>28573</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1125,12 +1125,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>15605</t>
+          <t>16430</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>36128</t>
+          <t>36272</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,52%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>493276</t>
+          <t>492280</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>503428</t>
+          <t>502611</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,58%</t>
+          <t>97,38%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,58%</t>
+          <t>99,42%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>494598</t>
+          <t>495192</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>512966</t>
+          <t>513246</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,43%</t>
+          <t>94,54%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,94%</t>
+          <t>97,99%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>993164</t>
+          <t>993020</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1013687</t>
+          <t>1012862</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,49%</t>
+          <t>96,48%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,48%</t>
+          <t>98,4%</t>
         </is>
       </c>
     </row>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2033</t>
+          <t>2034</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>12082</t>
+          <t>12532</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1438,7 +1438,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1453,12 +1453,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2970</t>
+          <t>2975</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>15664</t>
+          <t>15516</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1473,7 +1473,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>6988</t>
+          <t>7030</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>21316</t>
+          <t>23066</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,12 +1503,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,47%</t>
         </is>
       </c>
     </row>
@@ -1531,12 +1531,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>311964</t>
+          <t>311514</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>322013</t>
+          <t>322012</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,27%</t>
+          <t>96,13%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1566,12 +1566,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>325356</t>
+          <t>325504</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>338050</t>
+          <t>338045</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,41%</t>
+          <t>95,45%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>643750</t>
+          <t>642000</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>658078</t>
+          <t>658036</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,79%</t>
+          <t>96,53%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,95%</t>
+          <t>98,94%</t>
         </is>
       </c>
     </row>
@@ -1761,12 +1761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3235</t>
+          <t>2941</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>14315</t>
+          <t>13464</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1776,12 +1776,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1796,12 +1796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3950</t>
+          <t>3987</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>16314</t>
+          <t>15615</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1811,12 +1811,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>10102</t>
+          <t>9107</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>25046</t>
+          <t>25140</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,3%</t>
         </is>
       </c>
     </row>
@@ -1874,12 +1874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>359667</t>
+          <t>360518</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>370747</t>
+          <t>371041</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1889,12 +1889,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,17%</t>
+          <t>96,4%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,14%</t>
+          <t>99,21%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>372637</t>
+          <t>373336</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>385001</t>
+          <t>384964</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1924,12 +1924,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,81%</t>
+          <t>95,99%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,98%</t>
+          <t>98,97%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>737887</t>
+          <t>737793</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>752831</t>
+          <t>753826</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,72%</t>
+          <t>96,7%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,68%</t>
+          <t>98,81%</t>
         </is>
       </c>
     </row>
@@ -2104,12 +2104,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1954</t>
+          <t>1950</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>11638</t>
+          <t>12504</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2124,7 +2124,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2139,12 +2139,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1928</t>
+          <t>2090</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>13204</t>
+          <t>13191</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2154,7 +2154,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4925</t>
+          <t>5765</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>18518</t>
+          <t>18978</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2189,12 +2189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,39%</t>
         </is>
       </c>
     </row>
@@ -2217,12 +2217,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>200980</t>
+          <t>200114</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>210664</t>
+          <t>210668</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2232,7 +2232,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>94,53%</t>
+          <t>94,12%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2252,12 +2252,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>206387</t>
+          <t>206400</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>217663</t>
+          <t>217501</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2272,7 +2272,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,12%</t>
+          <t>99,05%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>413691</t>
+          <t>413231</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>427284</t>
+          <t>426444</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,12 +2302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,72%</t>
+          <t>95,61%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,86%</t>
+          <t>98,67%</t>
         </is>
       </c>
     </row>
@@ -2447,12 +2447,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3016</t>
+          <t>3029</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>13483</t>
+          <t>13393</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2462,12 +2462,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2482,12 +2482,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>4018</t>
+          <t>3989</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>15825</t>
+          <t>16464</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2497,12 +2497,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2517,12 +2517,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>9906</t>
+          <t>9194</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>25995</t>
+          <t>25033</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2532,12 +2532,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,53%</t>
         </is>
       </c>
     </row>
@@ -2560,12 +2560,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>260498</t>
+          <t>260588</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>270965</t>
+          <t>270952</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2575,12 +2575,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>95,08%</t>
+          <t>95,11%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,9%</t>
+          <t>98,89%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2595,12 +2595,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>262271</t>
+          <t>261632</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>274078</t>
+          <t>274107</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2610,12 +2610,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>94,31%</t>
+          <t>94,08%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>98,56%</t>
+          <t>98,57%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2630,12 +2630,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>526082</t>
+          <t>527044</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>542171</t>
+          <t>542883</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2645,12 +2645,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>95,29%</t>
+          <t>95,47%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,21%</t>
+          <t>98,33%</t>
         </is>
       </c>
     </row>
@@ -2790,12 +2790,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>4834</t>
+          <t>4759</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>18751</t>
+          <t>18529</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2805,12 +2805,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2825,12 +2825,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>7908</t>
+          <t>8673</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>25636</t>
+          <t>27486</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2840,12 +2840,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2860,12 +2860,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>15927</t>
+          <t>15261</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>37928</t>
+          <t>36653</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2875,12 +2875,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,7%</t>
         </is>
       </c>
     </row>
@@ -2903,12 +2903,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>644037</t>
+          <t>644259</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>657954</t>
+          <t>658029</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2918,12 +2918,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>97,17%</t>
+          <t>97,2%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>99,28%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2938,12 +2938,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>668217</t>
+          <t>666367</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>685945</t>
+          <t>685180</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2953,12 +2953,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>96,31%</t>
+          <t>96,04%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>98,86%</t>
+          <t>98,75%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2973,12 +2973,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1318713</t>
+          <t>1319988</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1340714</t>
+          <t>1341380</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2988,12 +2988,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>97,2%</t>
+          <t>97,3%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,83%</t>
+          <t>98,88%</t>
         </is>
       </c>
     </row>
@@ -3133,12 +3133,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>9331</t>
+          <t>9390</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>27041</t>
+          <t>26777</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3148,12 +3148,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3168,12 +3168,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>13830</t>
+          <t>13416</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>33501</t>
+          <t>32169</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3183,12 +3183,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3203,12 +3203,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>27658</t>
+          <t>27011</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>52721</t>
+          <t>51531</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3218,12 +3218,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,22%</t>
         </is>
       </c>
     </row>
@@ -3246,12 +3246,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>752057</t>
+          <t>752321</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>769767</t>
+          <t>769708</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3261,12 +3261,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>96,53%</t>
+          <t>96,56%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>98,8%</t>
+          <t>98,79%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>787894</t>
+          <t>789226</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>807565</t>
+          <t>807979</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3296,12 +3296,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>95,92%</t>
+          <t>96,08%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>98,32%</t>
+          <t>98,37%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3316,12 +3316,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1547772</t>
+          <t>1548962</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1572835</t>
+          <t>1573482</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3331,12 +3331,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>96,71%</t>
+          <t>96,78%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>98,27%</t>
+          <t>98,31%</t>
         </is>
       </c>
     </row>
@@ -3476,12 +3476,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>51408</t>
+          <t>50578</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>84834</t>
+          <t>83690</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3491,12 +3491,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3511,12 +3511,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>78185</t>
+          <t>77982</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>119660</t>
+          <t>119290</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3526,12 +3526,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3546,12 +3546,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>139010</t>
+          <t>139304</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>190369</t>
+          <t>190443</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3561,7 +3561,7 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -3589,12 +3589,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3341945</t>
+          <t>3343089</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3375371</t>
+          <t>3376201</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3604,12 +3604,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>97,52%</t>
+          <t>97,56%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>98,5%</t>
+          <t>98,52%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3624,12 +3624,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3434256</t>
+          <t>3434626</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3475731</t>
+          <t>3475934</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3639,12 +3639,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>96,63%</t>
+          <t>96,64%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>97,8%</t>
+          <t>97,81%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3659,12 +3659,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6790325</t>
+          <t>6790251</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6841684</t>
+          <t>6841390</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3679,7 +3679,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>98,01%</t>
+          <t>98,0%</t>
         </is>
       </c>
     </row>
@@ -4055,12 +4055,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5556</t>
+          <t>4705</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>19743</t>
+          <t>18391</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4090,12 +4090,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5571</t>
+          <t>5657</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>18582</t>
+          <t>18333</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>6,35%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4125,12 +4125,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>12622</t>
+          <t>12878</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>31553</t>
+          <t>32087</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4140,12 +4140,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,51%</t>
         </is>
       </c>
     </row>
@@ -4168,12 +4168,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>274018</t>
+          <t>275370</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>288205</t>
+          <t>289056</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,28%</t>
+          <t>93,74%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,11%</t>
+          <t>98,4%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>270121</t>
+          <t>270370</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>283132</t>
+          <t>283046</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,56%</t>
+          <t>93,65%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,07%</t>
+          <t>98,04%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4238,12 +4238,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>550911</t>
+          <t>550377</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>569842</t>
+          <t>569586</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4253,12 +4253,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,58%</t>
+          <t>94,49%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,83%</t>
+          <t>97,79%</t>
         </is>
       </c>
     </row>
@@ -4398,12 +4398,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1846</t>
+          <t>2126</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>12719</t>
+          <t>12724</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4413,7 +4413,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>11290</t>
+          <t>11002</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>28436</t>
+          <t>27662</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>15270</t>
+          <t>16095</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>35380</t>
+          <t>35951</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4483,12 +4483,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,51%</t>
         </is>
       </c>
     </row>
@@ -4511,12 +4511,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>489856</t>
+          <t>489851</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>500729</t>
+          <t>500449</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4531,7 +4531,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,63%</t>
+          <t>99,58%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4546,12 +4546,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>494648</t>
+          <t>495422</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>511794</t>
+          <t>512082</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,56%</t>
+          <t>94,71%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,84%</t>
+          <t>97,9%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4581,12 +4581,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>990279</t>
+          <t>989708</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1010389</t>
+          <t>1009564</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,55%</t>
+          <t>96,49%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,51%</t>
+          <t>98,43%</t>
         </is>
       </c>
     </row>
@@ -4741,12 +4741,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2497</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>13201</t>
+          <t>13784</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4756,12 +4756,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>6135</t>
+          <t>6516</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>20750</t>
+          <t>21771</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4791,12 +4791,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>10548</t>
+          <t>10681</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>29173</t>
+          <t>29942</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,57%</t>
         </is>
       </c>
     </row>
@@ -4854,12 +4854,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>305364</t>
+          <t>304781</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>316068</t>
+          <t>316546</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4869,12 +4869,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,86%</t>
+          <t>95,67%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,22%</t>
+          <t>99,37%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>315559</t>
+          <t>314538</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>330174</t>
+          <t>329793</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4904,12 +4904,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,83%</t>
+          <t>93,53%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,18%</t>
+          <t>98,06%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>625701</t>
+          <t>624932</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>644326</t>
+          <t>644193</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,55%</t>
+          <t>95,43%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,39%</t>
+          <t>98,37%</t>
         </is>
       </c>
     </row>
@@ -5084,12 +5084,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8475</t>
+          <t>7930</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>24588</t>
+          <t>23541</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>12344</t>
+          <t>12529</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>30402</t>
+          <t>29955</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5134,12 +5134,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>7,73%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>25279</t>
+          <t>25109</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>48330</t>
+          <t>49873</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5169,12 +5169,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>6,59%</t>
         </is>
       </c>
     </row>
@@ -5197,12 +5197,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>345376</t>
+          <t>346423</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>361489</t>
+          <t>362034</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5212,12 +5212,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,35%</t>
+          <t>93,64%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,71%</t>
+          <t>97,86%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>356881</t>
+          <t>357328</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>374939</t>
+          <t>374754</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5247,12 +5247,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,15%</t>
+          <t>92,27%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,81%</t>
+          <t>96,76%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>708917</t>
+          <t>707374</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>731968</t>
+          <t>732138</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5282,12 +5282,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,62%</t>
+          <t>93,41%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,66%</t>
+          <t>96,68%</t>
         </is>
       </c>
     </row>
@@ -5427,12 +5427,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1974</t>
+          <t>1948</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>11275</t>
+          <t>10993</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5442,12 +5442,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2980</t>
+          <t>2769</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>13223</t>
+          <t>13227</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5477,7 +5477,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>6374</t>
+          <t>6670</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>19087</t>
+          <t>21220</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,94%</t>
         </is>
       </c>
     </row>
@@ -5540,12 +5540,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>199946</t>
+          <t>200228</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>209247</t>
+          <t>209273</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5555,12 +5555,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>94,66%</t>
+          <t>94,8%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,07%</t>
+          <t>99,08%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>205364</t>
+          <t>205360</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>215607</t>
+          <t>215818</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5595,7 +5595,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,64%</t>
+          <t>98,73%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>410721</t>
+          <t>408588</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>423434</t>
+          <t>423138</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5625,12 +5625,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,56%</t>
+          <t>95,06%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,52%</t>
+          <t>98,45%</t>
         </is>
       </c>
     </row>
@@ -5770,12 +5770,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>833</t>
+          <t>834</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8688</t>
+          <t>8085</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5790,7 +5790,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>3887</t>
+          <t>3830</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>15989</t>
+          <t>15055</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5820,12 +5820,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>6413</t>
+          <t>5913</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>19907</t>
+          <t>19587</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5855,12 +5855,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,65%</t>
         </is>
       </c>
     </row>
@@ -5883,12 +5883,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>254435</t>
+          <t>255038</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>262290</t>
+          <t>262289</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5898,7 +5898,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>96,7%</t>
+          <t>96,93%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>257126</t>
+          <t>258060</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>269228</t>
+          <t>269285</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5933,12 +5933,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>94,15%</t>
+          <t>94,49%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>98,58%</t>
+          <t>98,6%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>516331</t>
+          <t>516651</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>529825</t>
+          <t>530325</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5968,12 +5968,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>96,29%</t>
+          <t>96,35%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,8%</t>
+          <t>98,9%</t>
         </is>
       </c>
     </row>
@@ -6113,12 +6113,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>12820</t>
+          <t>12686</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>32634</t>
+          <t>30759</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>20508</t>
+          <t>21167</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>43500</t>
+          <t>42886</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>38411</t>
+          <t>37727</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>68005</t>
+          <t>67867</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6198,12 +6198,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,04%</t>
         </is>
       </c>
     </row>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>623924</t>
+          <t>625799</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>643738</t>
+          <t>643872</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>95,03%</t>
+          <t>95,32%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,05%</t>
+          <t>98,07%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>647794</t>
+          <t>648408</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>670786</t>
+          <t>670127</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>93,71%</t>
+          <t>93,8%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>97,03%</t>
+          <t>96,94%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1279847</t>
+          <t>1279985</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1309441</t>
+          <t>1310125</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6311,12 +6311,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>94,95%</t>
+          <t>94,96%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>97,15%</t>
+          <t>97,2%</t>
         </is>
       </c>
     </row>
@@ -6456,12 +6456,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>11823</t>
+          <t>11737</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>27864</t>
+          <t>27804</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6491,12 +6491,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>24296</t>
+          <t>23617</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>50150</t>
+          <t>48637</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6506,12 +6506,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6526,12 +6526,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>38794</t>
+          <t>39469</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>70896</t>
+          <t>68574</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6541,12 +6541,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,27%</t>
         </is>
       </c>
     </row>
@@ -6569,12 +6569,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>750719</t>
+          <t>750779</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>766760</t>
+          <t>766846</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6584,12 +6584,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>96,42%</t>
+          <t>96,43%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>98,48%</t>
+          <t>98,49%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6604,12 +6604,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>776017</t>
+          <t>777530</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>801871</t>
+          <t>802550</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6619,12 +6619,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>93,93%</t>
+          <t>94,11%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>97,06%</t>
+          <t>97,14%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6639,12 +6639,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1533854</t>
+          <t>1536176</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1565956</t>
+          <t>1565281</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6654,12 +6654,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>95,58%</t>
+          <t>95,73%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>97,58%</t>
+          <t>97,54%</t>
         </is>
       </c>
     </row>
@@ -6799,12 +6799,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>68851</t>
+          <t>68484</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>106386</t>
+          <t>106829</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6814,12 +6814,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6834,12 +6834,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>119238</t>
+          <t>119676</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>166235</t>
+          <t>166461</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6849,12 +6849,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6869,12 +6869,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>200126</t>
+          <t>198200</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>260204</t>
+          <t>259201</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6884,12 +6884,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,74%</t>
         </is>
       </c>
     </row>
@@ -6912,12 +6912,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3287964</t>
+          <t>3287521</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3325499</t>
+          <t>3325866</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6927,12 +6927,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>96,87%</t>
+          <t>96,85%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>97,97%</t>
+          <t>97,98%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6947,12 +6947,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3378307</t>
+          <t>3378081</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3425304</t>
+          <t>3424866</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6962,12 +6962,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>95,31%</t>
+          <t>95,3%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>96,64%</t>
+          <t>96,62%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6982,12 +6982,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6678688</t>
+          <t>6679691</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6738766</t>
+          <t>6740692</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6997,12 +6997,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>96,25%</t>
+          <t>96,26%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>97,12%</t>
+          <t>97,14%</t>
         </is>
       </c>
     </row>
@@ -7373,32 +7373,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>12856</t>
+          <t>10971</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5973</t>
+          <t>5407</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>30394</t>
+          <t>21360</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7408,7 +7408,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>12156</t>
+          <t>11647</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -7418,22 +7418,22 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>18189</t>
+          <t>17881</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7443,32 +7443,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>25012</t>
+          <t>22618</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>16498</t>
+          <t>15036</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>41454</t>
+          <t>34173</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>5,38%</t>
         </is>
       </c>
     </row>
@@ -7486,32 +7486,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>298587</t>
+          <t>307874</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>281049</t>
+          <t>297485</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>305470</t>
+          <t>313438</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>95,87%</t>
+          <t>96,56%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>90,24%</t>
+          <t>93,3%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,08%</t>
+          <t>98,3%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7521,32 +7521,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>277479</t>
+          <t>304414</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>271446</t>
+          <t>298180</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>282088</t>
+          <t>308514</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>95,8%</t>
+          <t>96,31%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,72%</t>
+          <t>94,34%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,39%</t>
+          <t>97,61%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7556,32 +7556,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>576065</t>
+          <t>612288</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>559623</t>
+          <t>600733</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>584579</t>
+          <t>619870</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>95,84%</t>
+          <t>96,44%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,1%</t>
+          <t>94,62%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,26%</t>
+          <t>97,63%</t>
         </is>
       </c>
     </row>
@@ -7599,17 +7599,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7634,17 +7634,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7669,17 +7669,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7716,32 +7716,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>24509</t>
+          <t>23895</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>13397</t>
+          <t>13967</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>41654</t>
+          <t>40640</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>7,67%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7751,32 +7751,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>23084</t>
+          <t>24855</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>16631</t>
+          <t>16888</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>31915</t>
+          <t>33124</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7786,32 +7786,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>47593</t>
+          <t>48751</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>33860</t>
+          <t>36480</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>64574</t>
+          <t>64657</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>6,02%</t>
         </is>
       </c>
     </row>
@@ -7829,32 +7829,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>492884</t>
+          <t>505765</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>475739</t>
+          <t>489020</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>503996</t>
+          <t>515693</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>95,26%</t>
+          <t>95,49%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>91,95%</t>
+          <t>92,33%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,41%</t>
+          <t>97,36%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7864,32 +7864,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>490101</t>
+          <t>519808</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>481270</t>
+          <t>511539</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>496554</t>
+          <t>527775</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>95,5%</t>
+          <t>95,44%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,78%</t>
+          <t>93,92%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,76%</t>
+          <t>96,9%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7899,32 +7899,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>982985</t>
+          <t>1025572</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>966004</t>
+          <t>1009666</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>996718</t>
+          <t>1037843</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>95,38%</t>
+          <t>95,46%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,73%</t>
+          <t>93,98%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,71%</t>
+          <t>96,6%</t>
         </is>
       </c>
     </row>
@@ -7942,17 +7942,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>517393</t>
+          <t>529660</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>517393</t>
+          <t>529660</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>517393</t>
+          <t>529660</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7977,17 +7977,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>513185</t>
+          <t>544663</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>513185</t>
+          <t>544663</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>513185</t>
+          <t>544663</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -8012,17 +8012,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1030578</t>
+          <t>1074323</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1030578</t>
+          <t>1074323</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1030578</t>
+          <t>1074323</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -8059,32 +8059,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>13424</t>
+          <t>14097</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7933</t>
+          <t>9192</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>20983</t>
+          <t>22508</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8094,32 +8094,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>17661</t>
+          <t>17582</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>11610</t>
+          <t>11787</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>25910</t>
+          <t>25208</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8129,32 +8129,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>31084</t>
+          <t>31679</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>23090</t>
+          <t>22514</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>42305</t>
+          <t>41503</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,17%</t>
         </is>
       </c>
     </row>
@@ -8172,32 +8172,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>302626</t>
+          <t>301896</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>295067</t>
+          <t>293485</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>308117</t>
+          <t>306801</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>95,75%</t>
+          <t>95,54%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,36%</t>
+          <t>92,88%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,49%</t>
+          <t>97,09%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8207,32 +8207,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>331467</t>
+          <t>338799</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>323218</t>
+          <t>331173</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>337518</t>
+          <t>344594</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>94,94%</t>
+          <t>95,07%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>92,58%</t>
+          <t>92,93%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,67%</t>
+          <t>96,69%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8242,32 +8242,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>634094</t>
+          <t>640696</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>622873</t>
+          <t>630872</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>642088</t>
+          <t>649861</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>95,33%</t>
+          <t>95,29%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>93,64%</t>
+          <t>93,83%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,53%</t>
+          <t>96,65%</t>
         </is>
       </c>
     </row>
@@ -8285,17 +8285,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8320,17 +8320,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8355,17 +8355,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>665178</t>
+          <t>672375</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>665178</t>
+          <t>672375</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>665178</t>
+          <t>672375</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -8402,32 +8402,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>12054</t>
+          <t>12662</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5900</t>
+          <t>6145</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>29131</t>
+          <t>31936</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>8,56%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8437,32 +8437,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>76523</t>
+          <t>8139</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>6228</t>
+          <t>4396</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>227878</t>
+          <t>14233</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>16,09%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>47,9%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8472,32 +8472,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>88576</t>
+          <t>20800</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>17353</t>
+          <t>12947</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>270810</t>
+          <t>37611</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>11,24%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>34,35%</t>
+          <t>4,73%</t>
         </is>
       </c>
     </row>
@@ -8515,32 +8515,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>300503</t>
+          <t>360483</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>283426</t>
+          <t>341209</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>306657</t>
+          <t>367000</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>96,14%</t>
+          <t>96,61%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>90,68%</t>
+          <t>91,44%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,11%</t>
+          <t>98,35%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8550,32 +8550,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>399195</t>
+          <t>413822</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>247840</t>
+          <t>407728</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>469490</t>
+          <t>417565</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>83,91%</t>
+          <t>98,07%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>52,1%</t>
+          <t>96,63%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,69%</t>
+          <t>98,96%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8585,32 +8585,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>699698</t>
+          <t>774307</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>517464</t>
+          <t>757496</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>770921</t>
+          <t>782160</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>88,76%</t>
+          <t>97,38%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>65,65%</t>
+          <t>95,27%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,8%</t>
+          <t>98,37%</t>
         </is>
       </c>
     </row>
@@ -8628,17 +8628,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -8663,17 +8663,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -8698,17 +8698,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -8745,22 +8745,22 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>3430</t>
+          <t>3523</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>838</t>
+          <t>970</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>9165</t>
+          <t>9576</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -8770,7 +8770,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8780,32 +8780,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>10594</t>
+          <t>10093</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>6640</t>
+          <t>6248</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>19114</t>
+          <t>17010</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,21%</t>
+          <t>7,53%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8815,32 +8815,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>14025</t>
+          <t>13616</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>8346</t>
+          <t>8523</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>21818</t>
+          <t>21812</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,05%</t>
         </is>
       </c>
     </row>
@@ -8858,27 +8858,27 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>175312</t>
+          <t>202142</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>169577</t>
+          <t>196089</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>177904</t>
+          <t>204695</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>98,08%</t>
+          <t>98,29%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>94,87%</t>
+          <t>95,34%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -8893,32 +8893,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>196848</t>
+          <t>215875</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>188328</t>
+          <t>208958</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>200802</t>
+          <t>219720</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>94,89%</t>
+          <t>95,53%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>90,79%</t>
+          <t>92,47%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,8%</t>
+          <t>97,23%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8928,32 +8928,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>372159</t>
+          <t>418017</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>364366</t>
+          <t>409821</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>377838</t>
+          <t>423110</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>96,37%</t>
+          <t>96,85%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>94,35%</t>
+          <t>94,95%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,84%</t>
+          <t>98,03%</t>
         </is>
       </c>
     </row>
@@ -8971,17 +8971,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9006,17 +9006,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>207442</t>
+          <t>225968</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>207442</t>
+          <t>225968</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>207442</t>
+          <t>225968</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9041,17 +9041,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>386184</t>
+          <t>431633</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>386184</t>
+          <t>431633</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>386184</t>
+          <t>431633</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9088,32 +9088,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>9608</t>
+          <t>9601</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>5554</t>
+          <t>5721</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>15872</t>
+          <t>15677</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9123,32 +9123,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>13933</t>
+          <t>14180</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>9372</t>
+          <t>9263</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>20061</t>
+          <t>20408</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>7,76%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9158,32 +9158,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>23541</t>
+          <t>23782</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>17516</t>
+          <t>17585</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>32516</t>
+          <t>32265</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>6,04%</t>
         </is>
       </c>
     </row>
@@ -9201,32 +9201,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>260028</t>
+          <t>261106</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>253764</t>
+          <t>255030</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>264082</t>
+          <t>264986</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>96,44%</t>
+          <t>96,45%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>94,11%</t>
+          <t>94,21%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>97,94%</t>
+          <t>97,89%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9236,32 +9236,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>242454</t>
+          <t>248919</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>236326</t>
+          <t>242691</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>247015</t>
+          <t>253836</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>94,57%</t>
+          <t>94,61%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>92,18%</t>
+          <t>92,24%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>96,34%</t>
+          <t>96,48%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9271,32 +9271,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>502482</t>
+          <t>510024</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>493507</t>
+          <t>501541</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>508507</t>
+          <t>516221</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>95,52%</t>
+          <t>95,54%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>93,82%</t>
+          <t>93,96%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>96,67%</t>
+          <t>96,71%</t>
         </is>
       </c>
     </row>
@@ -9314,17 +9314,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -9349,17 +9349,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>256387</t>
+          <t>263099</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>256387</t>
+          <t>263099</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>256387</t>
+          <t>263099</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -9384,17 +9384,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>526023</t>
+          <t>533806</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>526023</t>
+          <t>533806</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>526023</t>
+          <t>533806</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -9431,32 +9431,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>23486</t>
+          <t>28778</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>13656</t>
+          <t>16912</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>40748</t>
+          <t>47390</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9466,32 +9466,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>48847</t>
+          <t>60291</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>24111</t>
+          <t>48548</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>70040</t>
+          <t>75381</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>9,78%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9501,32 +9501,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>72333</t>
+          <t>89069</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>46650</t>
+          <t>72050</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>96674</t>
+          <t>112254</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>7,55%</t>
         </is>
       </c>
     </row>
@@ -9544,32 +9544,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>597820</t>
+          <t>687653</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>580558</t>
+          <t>669041</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>607650</t>
+          <t>699519</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>96,22%</t>
+          <t>95,98%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>93,44%</t>
+          <t>93,39%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,8%</t>
+          <t>97,64%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9579,32 +9579,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>799627</t>
+          <t>710394</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>778434</t>
+          <t>695304</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>824363</t>
+          <t>722137</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>94,24%</t>
+          <t>92,18%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>91,75%</t>
+          <t>90,22%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>97,16%</t>
+          <t>93,7%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9614,32 +9614,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1397447</t>
+          <t>1398046</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1373106</t>
+          <t>1374861</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1423130</t>
+          <t>1415065</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>95,08%</t>
+          <t>94,01%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>93,42%</t>
+          <t>92,45%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>96,83%</t>
+          <t>95,16%</t>
         </is>
       </c>
     </row>
@@ -9657,17 +9657,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>621306</t>
+          <t>716431</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>621306</t>
+          <t>716431</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>621306</t>
+          <t>716431</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -9692,17 +9692,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>848474</t>
+          <t>770685</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>848474</t>
+          <t>770685</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>848474</t>
+          <t>770685</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -9727,17 +9727,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>1469780</t>
+          <t>1487115</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1469780</t>
+          <t>1487115</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1469780</t>
+          <t>1487115</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9774,32 +9774,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>27909</t>
+          <t>32354</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>12118</t>
+          <t>22042</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>45326</t>
+          <t>47381</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9809,32 +9809,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>26550</t>
+          <t>30908</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>19133</t>
+          <t>22734</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>35859</t>
+          <t>40391</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9844,32 +9844,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>54459</t>
+          <t>63263</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>33713</t>
+          <t>48303</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>71120</t>
+          <t>79630</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,89%</t>
         </is>
       </c>
     </row>
@@ -9887,32 +9887,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>900811</t>
+          <t>765718</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>883394</t>
+          <t>750691</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>916602</t>
+          <t>776030</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>96,99%</t>
+          <t>95,95%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>95,12%</t>
+          <t>94,06%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>98,7%</t>
+          <t>97,24%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9922,32 +9922,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>688842</t>
+          <t>799701</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>679533</t>
+          <t>790218</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>696259</t>
+          <t>807875</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>96,29%</t>
+          <t>96,28%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>94,99%</t>
+          <t>95,14%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>97,33%</t>
+          <t>97,26%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9957,32 +9957,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>1589653</t>
+          <t>1565418</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1572992</t>
+          <t>1549051</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1610399</t>
+          <t>1580378</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>96,69%</t>
+          <t>96,12%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>95,67%</t>
+          <t>95,11%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>97,95%</t>
+          <t>97,03%</t>
         </is>
       </c>
     </row>
@@ -10000,17 +10000,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -10035,17 +10035,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>715392</t>
+          <t>830609</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>715392</t>
+          <t>830609</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>715392</t>
+          <t>830609</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -10070,17 +10070,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>1644112</t>
+          <t>1628681</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1644112</t>
+          <t>1628681</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1644112</t>
+          <t>1628681</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -10117,32 +10117,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>127276</t>
+          <t>135881</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>95309</t>
+          <t>111411</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>159198</t>
+          <t>165220</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10152,32 +10152,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>229348</t>
+          <t>177696</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>152418</t>
+          <t>158583</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>508248</t>
+          <t>200886</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>13,9%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10187,32 +10187,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>356624</t>
+          <t>313578</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>273464</t>
+          <t>281706</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>620534</t>
+          <t>349650</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>8,73%</t>
+          <t>4,82%</t>
         </is>
       </c>
     </row>
@@ -10230,32 +10230,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>3328571</t>
+          <t>3392637</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3296649</t>
+          <t>3363298</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3360538</t>
+          <t>3417107</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>96,32%</t>
+          <t>96,15%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>95,39%</t>
+          <t>95,32%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>97,24%</t>
+          <t>96,84%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10265,32 +10265,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>3426011</t>
+          <t>3551731</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3147111</t>
+          <t>3528541</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3502941</t>
+          <t>3570844</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>93,73%</t>
+          <t>95,24%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>86,1%</t>
+          <t>94,61%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>95,83%</t>
+          <t>95,75%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10300,32 +10300,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>6754583</t>
+          <t>6944367</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6490673</t>
+          <t>6908295</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6837743</t>
+          <t>6976239</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>94,99%</t>
+          <t>95,68%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>91,27%</t>
+          <t>95,18%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>96,15%</t>
+          <t>96,12%</t>
         </is>
       </c>
     </row>
@@ -10343,17 +10343,17 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>3455847</t>
+          <t>3528518</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>3455847</t>
+          <t>3528518</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>3455847</t>
+          <t>3528518</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10378,17 +10378,17 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>3655359</t>
+          <t>3729427</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>3655359</t>
+          <t>3729427</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3655359</t>
+          <t>3729427</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -10413,17 +10413,17 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>7111207</t>
+          <t>7257945</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>7111207</t>
+          <t>7257945</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>7111207</t>
+          <t>7257945</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
